--- a/content.xlsx
+++ b/content.xlsx
@@ -428,7 +428,7 @@
         <v>Projects</v>
       </c>
       <c r="B3" t="str">
-        <v>5+</v>
+        <v>3+</v>
       </c>
       <c r="C3" t="str">
         <v>Major Projects</v>
@@ -469,7 +469,7 @@
         <v>p1</v>
       </c>
       <c r="B2" t="str">
-        <v>I am a highly motivated scholarship student pursuing a degree in Computer Science. My goal is to leverage my academic background to drive positive impact in the tech industry.</v>
+        <v>I am a highly motivated student pursuing a Bachelor of Science in Software Development. My goal is to leverage my academic background to drive positive impact in the tech industry.</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         <v>p2</v>
       </c>
       <c r="B3" t="str">
-        <v>Through various leadership roles and academic excellence, I have proven my dedication to continuous learning and community engagement.</v>
+        <v>Through various leadership roles and academic excellence across multiple institutions, I have proven my dedication to continuous learning and community engagement.</v>
       </c>
     </row>
   </sheetData>
@@ -510,13 +510,13 @@
         <v>Academics</v>
       </c>
       <c r="B2" t="str">
-        <v>Dean's Excellence Scholarship</v>
+        <v>American University of Phnom Penh (AUPP)</v>
       </c>
       <c r="C2" t="str">
-        <v>2023 - Present</v>
+        <v>Aug 2024 - Present</v>
       </c>
       <c r="D2" t="str">
-        <v>Awarded for outstanding academic performance and leadership potential among incoming freshmen.</v>
+        <v>Bachelor of Science in Software Development</v>
       </c>
     </row>
     <row r="3">
@@ -524,27 +524,27 @@
         <v>Academics</v>
       </c>
       <c r="B3" t="str">
-        <v>National Science Fair - 1st Place</v>
+        <v>TOUNGE LA' YAT COMMUNITY COLLEGE</v>
       </c>
       <c r="C3" t="str">
-        <v>2022</v>
+        <v>Jan 2022 - Dec 2023</v>
       </c>
       <c r="D3" t="str">
-        <v>Developed an AI model predicting crop yields to assist local farmers, winning top honors nationally.</v>
+        <v>Diploma in Social and Development Studies</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Experience</v>
+        <v>Academics</v>
       </c>
       <c r="B4" t="str">
-        <v>Software Engineering Intern</v>
+        <v>University of Yangon</v>
       </c>
       <c r="C4" t="str">
-        <v>Summer 2023</v>
+        <v>Dec 2018 - Mar 2020</v>
       </c>
       <c r="D4" t="str">
-        <v>Assisted in the backend development of a scalable REST API using Node.js and improved database query performance by 20%.</v>
+        <v>Bachelor of Science in Mathematics (2nd yr, incomplete)</v>
       </c>
     </row>
     <row r="5">
@@ -552,13 +552,13 @@
         <v>Experience</v>
       </c>
       <c r="B5" t="str">
-        <v>Past Community Development Leader</v>
+        <v>Junior Associate, Operations</v>
       </c>
       <c r="C5" t="str">
-        <v>2020 - 2022</v>
+        <v>June 2025 - Present</v>
       </c>
       <c r="D5" t="str">
-        <v>Spearheaded local neighborhood revitalization projects, organizing over 200 volunteers for after-school mentorship programs and community gardening.</v>
+        <v>AUPP Technology Center (ATC)</v>
       </c>
     </row>
   </sheetData>

--- a/content.xlsx
+++ b/content.xlsx
@@ -1,43 +1,133 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sawoolin/.gemini/antigravity/playground/warped-hawking/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB05D9A7-DAD0-3B4C-80A3-D59E34782663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17340" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Stats" sheetId="1" r:id="rId1"/>
     <sheet name="About" sheetId="2" r:id="rId2"/>
     <sheet name="Timeline" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>GPA</t>
+  </si>
+  <si>
+    <t>Cumulative GPA</t>
+  </si>
+  <si>
+    <t>Projects</t>
+  </si>
+  <si>
+    <t>3+</t>
+  </si>
+  <si>
+    <t>Major Projects</t>
+  </si>
+  <si>
+    <t>Volunteering</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>p1</t>
+  </si>
+  <si>
+    <t>p2</t>
+  </si>
+  <si>
+    <t>Through various leadership roles and academic excellence across multiple institutions, I have proven my dedication to continuous learning and community engagement.</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Academics</t>
+  </si>
+  <si>
+    <t>Aug 2024 - Present</t>
+  </si>
+  <si>
+    <t>TOUNGE LA' YAT COMMUNITY COLLEGE</t>
+  </si>
+  <si>
+    <t>Jan 2022 - Dec 2023</t>
+  </si>
+  <si>
+    <t>Diploma in Social and Development Studies</t>
+  </si>
+  <si>
+    <t>Dec 2018 - Mar 2020</t>
+  </si>
+  <si>
+    <t>Bachelor of Science in Mathematics (2nd yr, incomplete)</t>
+  </si>
+  <si>
+    <t>Experience</t>
+  </si>
+  <si>
+    <t>Junior Associate, Operations</t>
+  </si>
+  <si>
+    <t>June 2025 - Present</t>
+  </si>
+  <si>
+    <t>AUPP Technology Center (ATC)</t>
+  </si>
+  <si>
+    <t>2.5 yrs</t>
+  </si>
+  <si>
+    <t>Bachelor of Science in Cyber Security</t>
+  </si>
+  <si>
+    <t>UNIVERSITY OF YANGON</t>
+  </si>
+  <si>
+    <t>AMERICAN UNIVERSITY OF PHNOM PENH (AUPP)</t>
+  </si>
+  <si>
+    <t>I am a highly motivated student pursuing a Bachelor of Science in Cyber Security. My goal is to leverage my academic background to drive positive impact in the tech industry.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -66,14 +156,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,172 +497,178 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Metric</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Description</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>GPA</v>
-      </c>
-      <c r="B2" t="str">
-        <v>3.9</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Cumulative GPA</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Projects</v>
-      </c>
-      <c r="B3" t="str">
-        <v>3+</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Major Projects</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Volunteering</v>
-      </c>
-      <c r="B4" t="str">
-        <v>100h</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Volunteering</v>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>3.62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError sqref="A1:C1 A3:C3 A2 C2 A4 C4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Key</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Text</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>p1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>I am a highly motivated student pursuing a Bachelor of Science in Software Development. My goal is to leverage my academic background to drive positive impact in the tech industry.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>p2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Through various leadership roles and academic excellence across multiple institutions, I have proven my dedication to continuous learning and community engagement.</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError sqref="A1:B1 A3:B3 A2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Section</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Title</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Description</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Academics</v>
-      </c>
-      <c r="B2" t="str">
-        <v>American University of Phnom Penh (AUPP)</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Aug 2024 - Present</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Bachelor of Science in Software Development</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Academics</v>
-      </c>
-      <c r="B3" t="str">
-        <v>TOUNGE LA' YAT COMMUNITY COLLEGE</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Jan 2022 - Dec 2023</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Diploma in Social and Development Studies</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Academics</v>
-      </c>
-      <c r="B4" t="str">
-        <v>University of Yangon</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Dec 2018 - Mar 2020</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Bachelor of Science in Mathematics (2nd yr, incomplete)</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Experience</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Junior Associate, Operations</v>
-      </c>
-      <c r="C5" t="str">
-        <v>June 2025 - Present</v>
-      </c>
-      <c r="D5" t="str">
-        <v>AUPP Technology Center (ATC)</v>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError sqref="A1:D1 A3:D3 A2 A5:D5 A4 C4:D4 C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>